--- a/example.xlsx
+++ b/example.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Cole.Askey\Workspace\Source\AB\graphing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7514CC0A-9F8A-4A50-AB03-A04533CBB79A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C66D8331-503C-4D1A-B0D9-0C99D3A52654}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="3660" windowWidth="29040" windowHeight="15720" xr2:uid="{05900775-FAFB-4751-BB83-892DDF1C4885}"/>
+    <workbookView xWindow="-120" yWindow="2010" windowWidth="29040" windowHeight="16440" xr2:uid="{05900775-FAFB-4751-BB83-892DDF1C4885}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,51 +39,81 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="15">
-  <si>
-    <t>MP_IDs</t>
-  </si>
-  <si>
-    <t>Time|MP_Name</t>
-  </si>
-  <si>
-    <t>supDiagNoRollingMapMsg</t>
-  </si>
-  <si>
-    <t>supReplanMergePoint</t>
-  </si>
-  <si>
-    <t>supPlanRdyMsgCV</t>
-  </si>
-  <si>
-    <t>supMiscFlags2</t>
-  </si>
-  <si>
-    <t>10:07:21:273</t>
-  </si>
-  <si>
-    <t>0x00000000</t>
-  </si>
-  <si>
-    <t>10:07:21:280</t>
-  </si>
-  <si>
-    <t>10:07:21:283</t>
-  </si>
-  <si>
-    <t>10:07:21:474</t>
-  </si>
-  <si>
-    <t>10:07:21:477</t>
-  </si>
-  <si>
-    <t>10:07:21:703</t>
-  </si>
-  <si>
-    <t>10:07:21:706</t>
-  </si>
-  <si>
-    <t>10:07:21:710</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="25">
+  <si>
+    <t>Timestamp</t>
+  </si>
+  <si>
+    <t>MP8693</t>
+  </si>
+  <si>
+    <t>MP8741</t>
+  </si>
+  <si>
+    <t>MP8814</t>
+  </si>
+  <si>
+    <t>MP8817</t>
+  </si>
+  <si>
+    <t>MP8831</t>
+  </si>
+  <si>
+    <t>MP8835</t>
+  </si>
+  <si>
+    <t>ParameterName</t>
+  </si>
+  <si>
+    <t>data.rteAutoIndFencePos</t>
+  </si>
+  <si>
+    <t>data.ldsDistance</t>
+  </si>
+  <si>
+    <t>data.rteEffGrade[TRIPOPT_CURLOC]</t>
+  </si>
+  <si>
+    <t>data.rteVersion</t>
+  </si>
+  <si>
+    <t>data.rteRawGrade[TRIPOPT_CURLOC]</t>
+  </si>
+  <si>
+    <t>data.rteStatus</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 12:58:08.160</t>
+  </si>
+  <si>
+    <t>0x00000001</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 12:58:08.571</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 12:58:08.732</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 12:58:09.000</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 12:58:09.202</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 12:58:09.378</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 12:58:09.596</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 12:58:09.794</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 12:58:10.032</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 12:58:10.407</t>
   </si>
 </sst>
 </file>
@@ -455,177 +485,283 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D42EDEC1-3BC3-469B-9981-68D896C0CCD5}">
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1">
-        <v>8667</v>
-      </c>
-      <c r="C1">
-        <v>8669</v>
-      </c>
-      <c r="D1">
-        <v>8670</v>
-      </c>
-      <c r="E1">
-        <v>8671</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D2" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+      <c r="F2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3">
-        <v>0</v>
+        <v>14</v>
+      </c>
+      <c r="B3" t="s">
+        <v>15</v>
       </c>
       <c r="C3">
         <v>0</v>
       </c>
-      <c r="D3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>26.200000800000002</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <v>1122560</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4">
-        <v>0</v>
+        <v>16</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
       </c>
       <c r="C4">
         <v>0</v>
       </c>
-      <c r="D4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>26.200000800000002</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4">
+        <v>1122560</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5">
-        <v>0</v>
+        <v>17</v>
+      </c>
+      <c r="B5" t="s">
+        <v>15</v>
       </c>
       <c r="C5">
         <v>0</v>
       </c>
-      <c r="D5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>26.200000800000002</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <v>1122560</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6">
-        <v>0</v>
+        <v>18</v>
+      </c>
+      <c r="B6" t="s">
+        <v>15</v>
       </c>
       <c r="C6">
         <v>0</v>
       </c>
-      <c r="D6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E6" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>26.200000800000002</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <v>1122560</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>11</v>
-      </c>
-      <c r="B7">
-        <v>0</v>
+        <v>19</v>
+      </c>
+      <c r="B7" t="s">
+        <v>15</v>
       </c>
       <c r="C7">
         <v>0</v>
       </c>
-      <c r="D7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E7" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>26.200000800000002</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>1122560</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>12</v>
-      </c>
-      <c r="B8">
-        <v>0</v>
+        <v>20</v>
+      </c>
+      <c r="B8" t="s">
+        <v>15</v>
       </c>
       <c r="C8">
         <v>0</v>
       </c>
-      <c r="D8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E8" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <v>26.200000800000002</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <v>1122560</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>13</v>
-      </c>
-      <c r="B9">
-        <v>0</v>
+        <v>21</v>
+      </c>
+      <c r="B9" t="s">
+        <v>15</v>
       </c>
       <c r="C9">
         <v>0</v>
       </c>
-      <c r="D9" t="s">
-        <v>7</v>
-      </c>
-      <c r="E9" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9">
+        <v>26.200000800000002</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9">
+        <v>1122560</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>14</v>
-      </c>
-      <c r="B10">
-        <v>0</v>
+        <v>22</v>
+      </c>
+      <c r="B10" t="s">
+        <v>15</v>
       </c>
       <c r="C10">
         <v>0</v>
       </c>
-      <c r="D10" t="s">
-        <v>7</v>
-      </c>
-      <c r="E10" t="s">
-        <v>7</v>
+      <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <v>26.200000800000002</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>1122560</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>23</v>
+      </c>
+      <c r="B11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11">
+        <v>0</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11">
+        <v>26.200000800000002</v>
+      </c>
+      <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11">
+        <v>1122560</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>24</v>
+      </c>
+      <c r="B12" t="s">
+        <v>15</v>
+      </c>
+      <c r="C12">
+        <v>0</v>
+      </c>
+      <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="E12">
+        <v>26.200000800000002</v>
+      </c>
+      <c r="F12">
+        <v>0</v>
+      </c>
+      <c r="G12">
+        <v>1122560</v>
       </c>
     </row>
   </sheetData>
